--- a/reports/tables/DCA_Analysis_Final_Model.xlsx
+++ b/reports/tables/DCA_Analysis_Final_Model.xlsx
@@ -455,7 +455,7 @@
         <v>0.01</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0584572695125459</v>
+        <v>0.06070757829551799</v>
       </c>
       <c r="C2" t="n">
         <v>0.05926941102820499</v>
@@ -469,7 +469,7 @@
         <v>0.01482758620689655</v>
       </c>
       <c r="B3" t="n">
-        <v>0.05509111301461221</v>
+        <v>0.05680250511688063</v>
       </c>
       <c r="C3" t="n">
         <v>0.05465960065172438</v>
@@ -483,7 +483,7 @@
         <v>0.0196551724137931</v>
       </c>
       <c r="B4" t="n">
-        <v>0.05172538740130481</v>
+        <v>0.05289255516649963</v>
       </c>
       <c r="C4" t="n">
         <v>0.05000438939921792</v>
@@ -497,7 +497,7 @@
         <v>0.02448275862068965</v>
       </c>
       <c r="B5" t="n">
-        <v>0.04834292826214258</v>
+        <v>0.04684906801001591</v>
       </c>
       <c r="C5" t="n">
         <v>0.04530310323859192</v>
@@ -511,7 +511,7 @@
         <v>0.0293103448275862</v>
       </c>
       <c r="B6" t="n">
-        <v>0.04489290740261402</v>
+        <v>0.04411637822029033</v>
       </c>
       <c r="C6" t="n">
         <v>0.04055505472894372</v>
@@ -525,7 +525,7 @@
         <v>0.03413793103448275</v>
       </c>
       <c r="B7" t="n">
-        <v>0.04133185264654823</v>
+        <v>0.03550957213773259</v>
       </c>
       <c r="C7" t="n">
         <v>0.03575954268546111</v>
@@ -539,7 +539,7 @@
         <v>0.03896551724137931</v>
       </c>
       <c r="B8" t="n">
-        <v>0.0380475514758339</v>
+        <v>0.03334036526370641</v>
       </c>
       <c r="C8" t="n">
         <v>0.03091585183422194</v>
@@ -553,7 +553,7 @@
         <v>0.04379310344827586</v>
       </c>
       <c r="B9" t="n">
-        <v>0.03480680237344917</v>
+        <v>0.03114925511075029</v>
       </c>
       <c r="C9" t="n">
         <v>0.0260232524565368</v>
@@ -567,7 +567,7 @@
         <v>0.04862068965517241</v>
       </c>
       <c r="B10" t="n">
-        <v>0.03142995392572383</v>
+        <v>0.02893590824728937</v>
       </c>
       <c r="C10" t="n">
         <v>0.02108100002246341</v>
@@ -581,7 +581,7 @@
         <v>0.05344827586206896</v>
       </c>
       <c r="B11" t="n">
-        <v>0.02919881740212905</v>
+        <v>0.02669998443950171</v>
       </c>
       <c r="C11" t="n">
         <v>0.01608833481310622</v>
@@ -595,7 +595,7 @@
         <v>0.05827586206896551</v>
       </c>
       <c r="B12" t="n">
-        <v>0.0268583243325133</v>
+        <v>0.02444113647696557</v>
       </c>
       <c r="C12" t="n">
         <v>0.01104448153129863</v>
@@ -609,7 +609,7 @@
         <v>0.06310344827586206</v>
       </c>
       <c r="B13" t="n">
-        <v>0.02449371134904063</v>
+        <v>0.02215900999291637</v>
       </c>
       <c r="C13" t="n">
         <v>0.005948648900249015</v>
@@ -623,7 +623,7 @@
         <v>0.06793103448275861</v>
       </c>
       <c r="B14" t="n">
-        <v>0.02222668404297973</v>
+        <v>0.01985324327891772</v>
       </c>
       <c r="C14" t="n">
         <v>0.0008000292497138684</v>
@@ -637,7 +637,7 @@
         <v>0.07275862068965516</v>
       </c>
       <c r="B15" t="n">
-        <v>0.01982205561089195</v>
+        <v>0.01752346709374318</v>
       </c>
       <c r="C15" t="n">
         <v>-0.004402201910756187</v>
@@ -651,7 +651,7 @@
         <v>0.07758620689655171</v>
       </c>
       <c r="B16" t="n">
-        <v>0.01739225723633746</v>
+        <v>0.01180356611719031</v>
       </c>
       <c r="C16" t="n">
         <v>-0.009658886331971372</v>
@@ -665,7 +665,7 @@
         <v>0.08241379310344826</v>
       </c>
       <c r="B17" t="n">
-        <v>0.01474615970998674</v>
+        <v>0.01033225755484173</v>
       </c>
       <c r="C17" t="n">
         <v>-0.01497088347915199</v>
@@ -679,7 +679,7 @@
         <v>0.08724137931034481</v>
       </c>
       <c r="B18" t="n">
-        <v>0.002919774543286891</v>
+        <v>0.008845385471622058</v>
       </c>
       <c r="C18" t="n">
         <v>-0.02033907100038664</v>
@@ -693,7 +693,7 @@
         <v>0.09206896551724136</v>
       </c>
       <c r="B19" t="n">
-        <v>0.0008779178841415609</v>
+        <v>0.007342701607798461</v>
       </c>
       <c r="C19" t="n">
         <v>-0.02576434521003547</v>
@@ -707,7 +707,7 @@
         <v>0.09689655172413791</v>
       </c>
       <c r="B20" t="n">
-        <v>0.0003453694589787438</v>
+        <v>0.005823952395297097</v>
       </c>
       <c r="C20" t="n">
         <v>-0.0312476215876378</v>
@@ -721,7 +721,7 @@
         <v>0.1017241379310345</v>
       </c>
       <c r="B21" t="n">
-        <v>-0.0001929030951301602</v>
+        <v>0.007298167099091106</v>
       </c>
       <c r="C21" t="n">
         <v>-0.03678983529290726</v>
@@ -735,7 +735,7 @@
         <v>0.106551724137931</v>
       </c>
       <c r="B22" t="n">
-        <v>-0.002412034442119253</v>
+        <v>0.004656629345104528</v>
       </c>
       <c r="C22" t="n">
         <v>-0.04239194169742315</v>
@@ -749,7 +749,7 @@
         <v>0.1113793103448276</v>
       </c>
       <c r="B23" t="n">
-        <v>-0.002962035634127173</v>
+        <v>0.004381628749100568</v>
       </c>
       <c r="C23" t="n">
         <v>-0.04805491693365284</v>
@@ -763,7 +763,7 @@
         <v>0.1162068965517241</v>
       </c>
       <c r="B24" t="n">
-        <v>-0.003518045422848406</v>
+        <v>0.004103623854739951</v>
       </c>
       <c r="C24" t="n">
         <v>-0.05377975846196777</v>
@@ -777,7 +777,7 @@
         <v>0.1210344827586207</v>
       </c>
       <c r="B25" t="n">
-        <v>-0.003849507771629167</v>
+        <v>0.003822565160048971</v>
       </c>
       <c r="C25" t="n">
         <v>-0.059567485656345</v>
@@ -791,7 +791,7 @@
         <v>0.1258620689655172</v>
       </c>
       <c r="B26" t="n">
-        <v>-0.001701472517089061</v>
+        <v>0.003538402069519194</v>
       </c>
       <c r="C26" t="n">
         <v>-0.0654191404094767</v>
@@ -805,7 +805,7 @@
         <v>0.1306896551724138</v>
       </c>
       <c r="B27" t="n">
-        <v>-0.001850452846009766</v>
+        <v>0.003251082863743549</v>
       </c>
       <c r="C27" t="n">
         <v>-0.07133578775804182</v>
@@ -819,7 +819,7 @@
         <v>0.1355172413793103</v>
       </c>
       <c r="B28" t="n">
-        <v>-0.002001097095636405</v>
+        <v>0.00296055466803503</v>
       </c>
       <c r="C28" t="n">
         <v>-0.07731851652892836</v>
@@ -833,7 +833,7 @@
         <v>0.1403448275862069</v>
       </c>
       <c r="B29" t="n">
-        <v>-0.002153433298327444</v>
+        <v>0.002666763419988027</v>
       </c>
       <c r="C29" t="n">
         <v>-0.08336844000722961</v>
@@ -847,7 +847,7 @@
         <v>0.1451724137931034</v>
       </c>
       <c r="B30" t="n">
-        <v>-0.002307490119685424</v>
+        <v>-0.001233138936581522</v>
       </c>
       <c r="C30" t="n">
         <v>-0.0894866966268751</v>
@@ -861,7 +861,7 @@
         <v>0.15</v>
       </c>
       <c r="B31" t="n">
-        <v>-0.002463296876539561</v>
+        <v>-0.001477978125923737</v>
       </c>
       <c r="C31" t="n">
         <v>-0.09567445068479653</v>
